--- a/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Phylum_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Phylum_by_Sample_Type.xlsx
@@ -573,10 +573,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>29.2696693710857</v>
+        <v>29.2708263490043</v>
       </c>
       <c r="D2" t="n">
-        <v>0.323657020352679</v>
+        <v>0.323690875706401</v>
       </c>
     </row>
     <row r="3">
@@ -587,10 +587,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>13.5624767849073</v>
+        <v>13.5626620658277</v>
       </c>
       <c r="D3" t="n">
-        <v>0.164418843472401</v>
+        <v>0.164951302180931</v>
       </c>
     </row>
     <row r="4">
@@ -601,10 +601,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>10.3175885257203</v>
+        <v>10.3168263706702</v>
       </c>
       <c r="D4" t="n">
-        <v>0.122586489858399</v>
+        <v>0.122574627361324</v>
       </c>
     </row>
     <row r="5">
@@ -615,10 +615,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>9.30586667012119</v>
+        <v>9.30577787924505</v>
       </c>
       <c r="D5" t="n">
-        <v>0.167019150095391</v>
+        <v>0.16701269751572</v>
       </c>
     </row>
     <row r="6">
@@ -629,10 +629,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.06888660098701</v>
+        <v>4.0689240038311</v>
       </c>
       <c r="D6" t="n">
-        <v>0.313814867117275</v>
+        <v>0.313821955887357</v>
       </c>
     </row>
     <row r="7">
@@ -643,10 +643,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3.99447670452437</v>
+        <v>3.99479813533576</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0922713128025324</v>
+        <v>0.0922830964972073</v>
       </c>
     </row>
     <row r="8">
@@ -657,10 +657,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7243080649101</v>
+        <v>3.72399152550915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.053899320325139</v>
+        <v>0.0538939796108262</v>
       </c>
     </row>
     <row r="9">
@@ -671,10 +671,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.18513984798712</v>
+        <v>3.18497137478922</v>
       </c>
       <c r="D9" t="n">
-        <v>0.114016331705178</v>
+        <v>0.114008461300709</v>
       </c>
     </row>
     <row r="10">
@@ -685,10 +685,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.04891292336428</v>
+        <v>3.04910811408604</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0562950685147359</v>
+        <v>0.0562993834594735</v>
       </c>
     </row>
     <row r="11">
@@ -699,10 +699,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>2.90693837065784</v>
+        <v>2.9078237697701</v>
       </c>
       <c r="D11" t="n">
-        <v>0.848514761712234</v>
+        <v>0.848774383302174</v>
       </c>
     </row>
     <row r="12">
@@ -713,10 +713,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.92601490170582</v>
+        <v>1.92605377647559</v>
       </c>
       <c r="D12" t="n">
-        <v>0.117513743520371</v>
+        <v>0.117520824848877</v>
       </c>
     </row>
     <row r="13">
@@ -727,10 +727,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>1.75106759017128</v>
+        <v>1.75138898300309</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1667718000852</v>
+        <v>0.166801682503198</v>
       </c>
     </row>
     <row r="14">
@@ -741,10 +741,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>1.66227348891857</v>
+        <v>1.66241700859943</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0179556438162667</v>
+        <v>0.017957952356141</v>
       </c>
     </row>
     <row r="15">
@@ -755,10 +755,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1.55734061781472</v>
+        <v>1.55728726615353</v>
       </c>
       <c r="D15" t="n">
-        <v>0.522080141675004</v>
+        <v>0.522067960073351</v>
       </c>
     </row>
     <row r="16">
@@ -769,10 +769,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.23047170899452</v>
+        <v>1.230360372418</v>
       </c>
       <c r="D16" t="n">
-        <v>0.151613823845976</v>
+        <v>0.151602610044505</v>
       </c>
     </row>
     <row r="17">
@@ -783,10 +783,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.10164084860228</v>
+        <v>1.0999985026971</v>
       </c>
       <c r="D17" t="n">
-        <v>0.116595329532773</v>
+        <v>0.122485387874707</v>
       </c>
     </row>
     <row r="18">
@@ -797,10 +797,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.953034434585218</v>
+        <v>0.953081885062691</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0973706636466204</v>
+        <v>0.0973790540227632</v>
       </c>
     </row>
     <row r="19">
@@ -811,10 +811,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.848467110325538</v>
+        <v>0.84830527092907</v>
       </c>
       <c r="D19" t="n">
-        <v>0.289379225813157</v>
+        <v>0.289314746281158</v>
       </c>
     </row>
     <row r="20">
@@ -825,10 +825,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.546939917718448</v>
+        <v>0.5469106672692</v>
       </c>
       <c r="D20" t="n">
-        <v>0.236708808884444</v>
+        <v>0.23669411707758</v>
       </c>
     </row>
     <row r="21">
@@ -839,10 +839,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.430293030354796</v>
+        <v>0.430362935082194</v>
       </c>
       <c r="D21" t="n">
-        <v>0.106578730709796</v>
+        <v>0.106595560404305</v>
       </c>
     </row>
     <row r="22">
@@ -853,10 +853,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.419048522431741</v>
+        <v>0.419020322211645</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0232657073408555</v>
+        <v>0.0232625777419894</v>
       </c>
     </row>
     <row r="23">
@@ -867,10 +867,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.408266721626298</v>
+        <v>0.408321587683296</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0234940178096526</v>
+        <v>0.0234985282277792</v>
       </c>
     </row>
     <row r="24">
@@ -881,10 +881,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.372071007050711</v>
+        <v>0.372087649602625</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0183126347282866</v>
+        <v>0.018315556326914</v>
       </c>
     </row>
     <row r="25">
@@ -895,10 +895,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.346401561761411</v>
+        <v>0.346406996330817</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00848242083577107</v>
+        <v>0.00848308271124754</v>
       </c>
     </row>
     <row r="26">
@@ -909,10 +909,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.310150166875274</v>
+        <v>0.310114714012385</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0685769544517772</v>
+        <v>0.0685672363066828</v>
       </c>
     </row>
     <row r="27">
@@ -923,10 +923,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.295566559308626</v>
+        <v>0.295571086745162</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00808169739661992</v>
+        <v>0.00808183984791037</v>
       </c>
     </row>
     <row r="28">
@@ -937,10 +937,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.268374612534452</v>
+        <v>0.268367880451845</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00445395544917261</v>
+        <v>0.0044535770587391</v>
       </c>
     </row>
     <row r="29">
@@ -951,10 +951,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.242674225434993</v>
+        <v>0.242650323142323</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0224444037160852</v>
+        <v>0.0224418613647339</v>
       </c>
     </row>
     <row r="30">
@@ -965,10 +965,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.235791615880213</v>
+        <v>0.235759726724195</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0947939764946072</v>
+        <v>0.0947801490926459</v>
       </c>
     </row>
     <row r="31">
@@ -979,10 +979,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.228626419407055</v>
+        <v>0.228594367045524</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0299715373829527</v>
+        <v>0.0299670122309286</v>
       </c>
     </row>
     <row r="32">
@@ -993,10 +993,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.213394528600517</v>
+        <v>0.213419785319753</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0615196028841004</v>
+        <v>0.0615402836652481</v>
       </c>
     </row>
     <row r="33">
@@ -1007,10 +1007,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.184825372319607</v>
+        <v>0.18480018114175</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0604408082587919</v>
+        <v>0.0604306433345011</v>
       </c>
     </row>
     <row r="34">
@@ -1021,10 +1021,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.18446535613716</v>
+        <v>0.18449359375152</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00414895993143551</v>
+        <v>0.00414959037998375</v>
       </c>
     </row>
     <row r="35">
@@ -1035,10 +1035,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.112034240751219</v>
+        <v>0.112029676930257</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00554861862622549</v>
+        <v>0.00554800524943868</v>
       </c>
     </row>
     <row r="36">
@@ -1049,10 +1049,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0931332790647367</v>
+        <v>0.0931309996902721</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0327415527241503</v>
+        <v>0.0327398335275147</v>
       </c>
     </row>
     <row r="37">
@@ -1063,10 +1063,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0904120440215771</v>
+        <v>0.0904003250131124</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00899418206847615</v>
+        <v>0.00899305994560171</v>
       </c>
     </row>
     <row r="38">
@@ -1077,7 +1077,7 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0828081315444811</v>
+        <v>0.082792415700007</v>
       </c>
       <c r="D38"/>
     </row>
@@ -1089,10 +1089,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07513007830488</v>
+        <v>0.0751270586034985</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00978986799512828</v>
+        <v>0.00978935660872495</v>
       </c>
     </row>
     <row r="40">
@@ -1103,10 +1103,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0555176044620979</v>
+        <v>0.0555219006253551</v>
       </c>
       <c r="D40" t="n">
-        <v>0.010882824261015</v>
+        <v>0.0108834020325943</v>
       </c>
     </row>
     <row r="41">
@@ -1117,10 +1117,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0443534406113147</v>
+        <v>0.044345580038103</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00408391518117944</v>
+        <v>0.00408301381369857</v>
       </c>
     </row>
     <row r="42">
@@ -1131,10 +1131,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0439272059655816</v>
+        <v>0.0439311193068667</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00281672021647584</v>
+        <v>0.00281725961473784</v>
       </c>
     </row>
     <row r="43">
@@ -1145,7 +1145,7 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0425454373998597</v>
+        <v>0.0425428850299084</v>
       </c>
       <c r="D43"/>
     </row>
@@ -1157,10 +1157,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0422022374185856</v>
+        <v>0.042212466894678</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00704739422470973</v>
+        <v>0.00704998638812337</v>
       </c>
     </row>
     <row r="45">
@@ -1171,10 +1171,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0401099282992982</v>
+        <v>0.0401154360391381</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00899770989979867</v>
+        <v>0.00899976873991183</v>
       </c>
     </row>
     <row r="46">
@@ -1185,10 +1185,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0397407192602098</v>
+        <v>0.0397402698905676</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00804735726344126</v>
+        <v>0.00804510732230997</v>
       </c>
     </row>
     <row r="47">
@@ -1199,10 +1199,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0345161871410933</v>
+        <v>0.0345189461904412</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00893760982438653</v>
+        <v>0.00893874389584192</v>
       </c>
     </row>
     <row r="48">
@@ -1213,10 +1213,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0240757178501265</v>
+        <v>0.0240772699490756</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00316824594110922</v>
+        <v>0.00316770989894922</v>
       </c>
     </row>
     <row r="49">
@@ -1227,10 +1227,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0189050723134356</v>
+        <v>0.0189074176699697</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00270797388873265</v>
+        <v>0.00270831467486109</v>
       </c>
     </row>
     <row r="50">
@@ -1241,10 +1241,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.015449903512412</v>
+        <v>0.0154465809187106</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00589527197923556</v>
+        <v>0.0058945862179202</v>
       </c>
     </row>
     <row r="51">
@@ -1255,10 +1255,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0102809022265025</v>
+        <v>0.0102788203664386</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00662758978737952</v>
+        <v>0.00662641101662855</v>
       </c>
     </row>
     <row r="52">
@@ -1269,7 +1269,7 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00880533662757085</v>
+        <v>0.00880743994783173</v>
       </c>
       <c r="D52"/>
     </row>
@@ -1281,10 +1281,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00751019018255811</v>
+        <v>0.00751056931079806</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00155233406502311</v>
+        <v>0.00155267126757225</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00730959158723154</v>
+        <v>0.00730789592149665</v>
       </c>
       <c r="D54"/>
     </row>
@@ -1307,7 +1307,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00305726011193323</v>
+        <v>0.00305638642701374</v>
       </c>
       <c r="D55"/>
     </row>
@@ -1319,7 +1319,7 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00177541715051518</v>
+        <v>0.00177542785482386</v>
       </c>
       <c r="D56"/>
     </row>
@@ -1331,10 +1331,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00172227795480832</v>
+        <v>0.00172358291115443</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00017926116801792</v>
+        <v>0.00017928492614524</v>
       </c>
     </row>
     <row r="58">
@@ -1345,7 +1345,7 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.00165785321964755</v>
+        <v>0.00165941172007079</v>
       </c>
       <c r="D58"/>
     </row>
@@ -1357,7 +1357,7 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00110359122898367</v>
+        <v>0.00110308708677645</v>
       </c>
       <c r="D59"/>
     </row>
@@ -1369,7 +1369,7 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.000452168964875471</v>
+        <v>0.00045256004142569</v>
       </c>
       <c r="D60"/>
     </row>
@@ -1406,10 +1406,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>23.6761079288351</v>
+        <v>23.9587004222647</v>
       </c>
       <c r="D2" t="n">
-        <v>0.255558900822582</v>
+        <v>0.259325109089139</v>
       </c>
     </row>
     <row r="3">
@@ -1420,10 +1420,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>12.080153452907</v>
+        <v>12.3045999647372</v>
       </c>
       <c r="D3" t="n">
-        <v>1.68039969508582</v>
+        <v>1.71232912995347</v>
       </c>
     </row>
     <row r="4">
@@ -1431,13 +1431,13 @@
         <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>9.40053019487132</v>
+        <v>9.15105151364344</v>
       </c>
       <c r="D4" t="n">
-        <v>0.630555766980555</v>
+        <v>0.0836314974382178</v>
       </c>
     </row>
     <row r="5">
@@ -1445,13 +1445,13 @@
         <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>9.05525136840053</v>
+        <v>9.08294292291887</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0825799999700175</v>
+        <v>0.602325234484184</v>
       </c>
     </row>
     <row r="6">
@@ -1462,10 +1462,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>8.28770331205634</v>
+        <v>8.40161069868793</v>
       </c>
       <c r="D6" t="n">
-        <v>0.668281225283254</v>
+        <v>0.677190845957553</v>
       </c>
     </row>
     <row r="7">
@@ -1476,10 +1476,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>8.18144803395273</v>
+        <v>8.27506015303526</v>
       </c>
       <c r="D7" t="n">
-        <v>0.166359229091868</v>
+        <v>0.168366418761563</v>
       </c>
     </row>
     <row r="8">
@@ -1490,10 +1490,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>4.59508593858663</v>
+        <v>4.6562194681692</v>
       </c>
       <c r="D8" t="n">
-        <v>0.100439062617691</v>
+        <v>0.101758636896761</v>
       </c>
     </row>
     <row r="9">
@@ -1501,13 +1501,13 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>3.76132783638937</v>
+        <v>3.25325299906447</v>
       </c>
       <c r="D9" t="n">
-        <v>0.302271592451519</v>
+        <v>0.0630229464333589</v>
       </c>
     </row>
     <row r="10">
@@ -1515,13 +1515,13 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>3.20948650884179</v>
+        <v>2.98389048871967</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0621886786915914</v>
+        <v>0.293331751281884</v>
       </c>
     </row>
     <row r="11">
@@ -1532,10 +1532,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>2.690572949422</v>
+        <v>2.72737276492426</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0324620919657968</v>
+        <v>0.0329264894368896</v>
       </c>
     </row>
     <row r="12">
@@ -1546,10 +1546,10 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>2.61680289687953</v>
+        <v>2.65555052776712</v>
       </c>
       <c r="D12" t="n">
-        <v>0.282181133600363</v>
+        <v>0.286479070820764</v>
       </c>
     </row>
     <row r="13">
@@ -1560,10 +1560,10 @@
         <v>38</v>
       </c>
       <c r="C13" t="n">
-        <v>2.23819930882622</v>
+        <v>2.24662878343741</v>
       </c>
       <c r="D13" t="n">
-        <v>0.125198004652938</v>
+        <v>0.126032458507861</v>
       </c>
     </row>
     <row r="14">
@@ -1574,10 +1574,10 @@
         <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6265877490813</v>
+        <v>1.64857236206123</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0536567655594637</v>
+        <v>0.0543763155604352</v>
       </c>
     </row>
     <row r="15">
@@ -1588,10 +1588,10 @@
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>1.508592975179</v>
+        <v>1.51460726307645</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0393988585022581</v>
+        <v>0.0397095256164362</v>
       </c>
     </row>
     <row r="16">
@@ -1602,10 +1602,10 @@
         <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>1.32599225763874</v>
+        <v>1.34225464279709</v>
       </c>
       <c r="D16" t="n">
-        <v>0.078057535367562</v>
+        <v>0.079113798191263</v>
       </c>
     </row>
     <row r="17">
@@ -1616,10 +1616,10 @@
         <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>1.02469258838476</v>
+        <v>1.03850212572762</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0613034377823126</v>
+        <v>0.0621006698155336</v>
       </c>
     </row>
     <row r="18">
@@ -1630,10 +1630,10 @@
         <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>0.55787953554294</v>
+        <v>0.565248583401867</v>
       </c>
       <c r="D18" t="n">
-        <v>0.220142187115431</v>
+        <v>0.223054136267222</v>
       </c>
     </row>
     <row r="19">
@@ -1644,10 +1644,10 @@
         <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>0.548681852072913</v>
+        <v>0.544317356484604</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0251147427536046</v>
+        <v>0.0243983685959649</v>
       </c>
     </row>
     <row r="20">
@@ -1658,10 +1658,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.47770341579368</v>
+        <v>0.484635342954498</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0768589214136416</v>
+        <v>0.0780168403652889</v>
       </c>
     </row>
     <row r="21">
@@ -1672,10 +1672,10 @@
         <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>0.410087105566308</v>
+        <v>0.410673850905878</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00877913929635985</v>
+        <v>0.0087179727846737</v>
       </c>
     </row>
     <row r="22">
@@ -1686,10 +1686,10 @@
         <v>36</v>
       </c>
       <c r="C22" t="n">
-        <v>0.401368976897267</v>
+        <v>0.406784578837727</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0284640790427565</v>
+        <v>0.0288408938510205</v>
       </c>
     </row>
     <row r="23">
@@ -1700,10 +1700,10 @@
         <v>30</v>
       </c>
       <c r="C23" t="n">
-        <v>0.274540482711706</v>
+        <v>0.278446348778541</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0159679648328081</v>
+        <v>0.0161832301591396</v>
       </c>
     </row>
     <row r="24">
@@ -1714,10 +1714,10 @@
         <v>41</v>
       </c>
       <c r="C24" t="n">
-        <v>0.24980593987073</v>
+        <v>0.253337831876229</v>
       </c>
       <c r="D24" t="n">
-        <v>0.137157739177543</v>
+        <v>0.139043368674031</v>
       </c>
     </row>
     <row r="25">
@@ -1728,10 +1728,10 @@
         <v>37</v>
       </c>
       <c r="C25" t="n">
-        <v>0.203780796758657</v>
+        <v>0.206857166723723</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00669328988185144</v>
+        <v>0.00680462382491655</v>
       </c>
     </row>
     <row r="26">
@@ -1742,10 +1742,10 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.201740253839049</v>
+        <v>0.200479419853574</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0127362299980534</v>
+        <v>0.0123753696026022</v>
       </c>
     </row>
     <row r="27">
@@ -1756,10 +1756,10 @@
         <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>0.138638720020316</v>
+        <v>0.1406423844885</v>
       </c>
       <c r="D27" t="n">
-        <v>0.03702259070827</v>
+        <v>0.0375469334006258</v>
       </c>
     </row>
     <row r="28">
@@ -1770,10 +1770,10 @@
         <v>14</v>
       </c>
       <c r="C28" t="n">
-        <v>0.130250407027724</v>
+        <v>0.131996507405069</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0202301973681645</v>
+        <v>0.0204959555924036</v>
       </c>
     </row>
     <row r="29">
@@ -1784,10 +1784,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.127142066876816</v>
+        <v>0.128980575307602</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00802171919862632</v>
+        <v>0.00813957118733485</v>
       </c>
     </row>
     <row r="30">
@@ -1798,10 +1798,10 @@
         <v>18</v>
       </c>
       <c r="C30" t="n">
-        <v>0.114685645244818</v>
+        <v>0.116360950573543</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0245655527752233</v>
+        <v>0.0249510391309751</v>
       </c>
     </row>
     <row r="31">
@@ -1812,10 +1812,10 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>0.102923804598766</v>
+        <v>0.104478448570681</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0576833500162469</v>
+        <v>0.0585564615459557</v>
       </c>
     </row>
     <row r="32">
@@ -1826,10 +1826,10 @@
         <v>28</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0976664344296023</v>
+        <v>0.0986092963616454</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00231007176757483</v>
+        <v>0.00231903468806524</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1840,10 @@
         <v>45</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0916016417953377</v>
+        <v>0.0900956608547697</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00845852166798351</v>
+        <v>0.00800482913878275</v>
       </c>
     </row>
     <row r="34">
@@ -1854,7 +1854,7 @@
         <v>65</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0794332681635743</v>
+        <v>0.080520581383524</v>
       </c>
       <c r="D34"/>
     </row>
@@ -1866,10 +1866,10 @@
         <v>22</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0604233606267015</v>
+        <v>0.0612506592225904</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0195724390892119</v>
+        <v>0.0198458036605469</v>
       </c>
     </row>
     <row r="36">
@@ -1877,13 +1877,13 @@
         <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0563901443258622</v>
+        <v>0.0559530158151055</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0102407849022143</v>
+        <v>0.0181254687030527</v>
       </c>
     </row>
     <row r="37">
@@ -1891,13 +1891,13 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0551314705330944</v>
+        <v>0.0547964171152686</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0178571239040387</v>
+        <v>0.00965221378338962</v>
       </c>
     </row>
     <row r="38">
@@ -1908,10 +1908,10 @@
         <v>50</v>
       </c>
       <c r="C38" t="n">
-        <v>0.054303937705371</v>
+        <v>0.0533686607917045</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00672248951769872</v>
+        <v>0.00643239255487694</v>
       </c>
     </row>
     <row r="39">
@@ -1922,10 +1922,10 @@
         <v>51</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0397822219382303</v>
+        <v>0.040320883277201</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00534862034970084</v>
+        <v>0.00542102753250326</v>
       </c>
     </row>
     <row r="40">
@@ -1936,10 +1936,10 @@
         <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>0.037239979900959</v>
+        <v>0.0377640386805224</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0046423246437133</v>
+        <v>0.00470575262805252</v>
       </c>
     </row>
     <row r="41">
@@ -1950,10 +1950,10 @@
         <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0348180849197775</v>
+        <v>0.0352781756278973</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00725469252960738</v>
+        <v>0.00734905707440079</v>
       </c>
     </row>
     <row r="42">
@@ -1964,10 +1964,10 @@
         <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>0.026197242278464</v>
+        <v>0.0265918454486327</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00343924879521813</v>
+        <v>0.0034928416871226</v>
       </c>
     </row>
     <row r="43">
@@ -1978,10 +1978,10 @@
         <v>23</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0258934382961188</v>
+        <v>0.0262491258921024</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00900491434123902</v>
+        <v>0.00912560058852466</v>
       </c>
     </row>
     <row r="44">
@@ -1992,10 +1992,10 @@
         <v>49</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0206525689373119</v>
+        <v>0.0209610588989829</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00350135414698677</v>
+        <v>0.00355797137959163</v>
       </c>
     </row>
     <row r="45">
@@ -2006,10 +2006,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0170419853711769</v>
+        <v>0.0172826710829321</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00815725481652204</v>
+        <v>0.00826073395968249</v>
       </c>
     </row>
     <row r="46">
@@ -2020,10 +2020,10 @@
         <v>46</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0141565493962822</v>
+        <v>0.0143620097986818</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00493869471385782</v>
+        <v>0.00500606145536849</v>
       </c>
     </row>
     <row r="47">
@@ -2034,10 +2034,10 @@
         <v>39</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0140572294145009</v>
+        <v>0.0142599484370969</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00206737573346722</v>
+        <v>0.00209716350582463</v>
       </c>
     </row>
     <row r="48">
@@ -2048,10 +2048,10 @@
         <v>57</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0132393793539659</v>
+        <v>0.0134358834712381</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00029825902958435</v>
+        <v>0.000289288718725805</v>
       </c>
     </row>
     <row r="49">
@@ -2062,10 +2062,10 @@
         <v>42</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0123475621192286</v>
+        <v>0.0125175053335992</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00139722014161033</v>
+        <v>0.00141592241424564</v>
       </c>
     </row>
     <row r="50">
@@ -2076,7 +2076,7 @@
         <v>66</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00685213338398429</v>
+        <v>0.00695981874693831</v>
       </c>
       <c r="D50"/>
     </row>
@@ -2088,10 +2088,10 @@
         <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>0.00657396868162012</v>
+        <v>0.00667159769397817</v>
       </c>
       <c r="D51" t="n">
-        <v>0.000190007450251373</v>
+        <v>0.000194466533363914</v>
       </c>
     </row>
     <row r="52">
@@ -2102,10 +2102,10 @@
         <v>43</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00307264568961657</v>
+        <v>0.00311393073780596</v>
       </c>
       <c r="D52" t="n">
-        <v>0.000565691955411315</v>
+        <v>0.000573125122682993</v>
       </c>
     </row>
     <row r="53">
@@ -2116,10 +2116,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00289852776366709</v>
+        <v>0.00294004626848082</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00136424539014174</v>
+        <v>0.00138350924121507</v>
       </c>
     </row>
     <row r="54">
@@ -2130,10 +2130,10 @@
         <v>67</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00255458899779847</v>
+        <v>0.0025902459692076</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0015350900421055</v>
+        <v>0.00155677877880343</v>
       </c>
     </row>
     <row r="55">
@@ -2144,10 +2144,10 @@
         <v>62</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00204151692577556</v>
+        <v>0.00206870863898209</v>
       </c>
       <c r="D55" t="n">
-        <v>0.000564269459936274</v>
+        <v>0.00057207264784769</v>
       </c>
     </row>
     <row r="56">
@@ -2158,10 +2158,10 @@
         <v>44</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00166890227246445</v>
+        <v>0.00169459005110832</v>
       </c>
       <c r="D56" t="n">
-        <v>0.000286642957455543</v>
+        <v>0.000290784817273509</v>
       </c>
     </row>
     <row r="57">
@@ -2172,10 +2172,10 @@
         <v>63</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00157554091664521</v>
+        <v>0.00159601102201996</v>
       </c>
       <c r="D57" t="n">
-        <v>0.000571561856747628</v>
+        <v>0.000578987834272048</v>
       </c>
     </row>
     <row r="58">
@@ -2186,10 +2186,10 @@
         <v>59</v>
       </c>
       <c r="C58" t="n">
-        <v>0.000950057074068544</v>
+        <v>0.000963996693343051</v>
       </c>
       <c r="D58" t="n">
-        <v>0.000155571131975538</v>
+        <v>0.000156710025883741</v>
       </c>
     </row>
     <row r="59">
@@ -2200,10 +2200,10 @@
         <v>68</v>
       </c>
       <c r="C59" t="n">
-        <v>0.000891215642693053</v>
+        <v>0.000904187632715698</v>
       </c>
       <c r="D59" t="n">
-        <v>0.000223268882374268</v>
+        <v>0.000227154640111694</v>
       </c>
     </row>
     <row r="60">
@@ -2214,10 +2214,10 @@
         <v>47</v>
       </c>
       <c r="C60" t="n">
-        <v>0.000809972069479376</v>
+        <v>0.000822613993985233</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0000171371325066804</v>
+        <v>0.0000183242180324971</v>
       </c>
     </row>
     <row r="61">
@@ -2228,7 +2228,7 @@
         <v>61</v>
       </c>
       <c r="C61" t="n">
-        <v>0.000730046269315004</v>
+        <v>0.000742375249378426</v>
       </c>
       <c r="D61"/>
     </row>
@@ -2240,7 +2240,7 @@
         <v>58</v>
       </c>
       <c r="C62" t="n">
-        <v>0.000631700293700563</v>
+        <v>0.000640604082168272</v>
       </c>
       <c r="D62"/>
     </row>
@@ -2252,7 +2252,7 @@
         <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>0.000441539913237802</v>
+        <v>0.000447682861862285</v>
       </c>
       <c r="D63"/>
     </row>
@@ -2264,7 +2264,7 @@
         <v>60</v>
       </c>
       <c r="C64" t="n">
-        <v>0.000166841526938102</v>
+        <v>0.000169705670329334</v>
       </c>
       <c r="D64"/>
     </row>
